--- a/data/trans_orig/P36B08_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>224427</t>
+          <t>226638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>266966</t>
+          <t>269651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226501</t>
+          <t>225314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268689</t>
+          <t>266298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>461552</t>
+          <t>464901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>522033</t>
+          <t>523123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227098</t>
+          <t>224413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269637</t>
+          <t>267426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197740</t>
+          <t>200131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>241115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438460</t>
+          <t>437370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498941</t>
+          <t>495592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>427865</t>
+          <t>428137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>482804</t>
+          <t>481931</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>407268</t>
+          <t>407688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>454986</t>
+          <t>452896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>852097</t>
+          <t>850741</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>922447</t>
+          <t>922146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>252685</t>
+          <t>253558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307624</t>
+          <t>307352</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>170508</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218226</t>
+          <t>217806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>438535</t>
+          <t>438836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>508885</t>
+          <t>510241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>367675</t>
+          <t>367534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>417896</t>
+          <t>415835</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>473304</t>
+          <t>474112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>523123</t>
+          <t>522526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848840</t>
+          <t>853174</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>922123</t>
+          <t>924397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220772</t>
+          <t>222833</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>270993</t>
+          <t>271134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166621</t>
+          <t>167218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216440</t>
+          <t>215632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406289</t>
+          <t>404015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479572</t>
+          <t>475238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>311524</t>
+          <t>310166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>359425</t>
+          <t>355554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>377876</t>
+          <t>378321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>415629</t>
+          <t>416415</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>701772</t>
+          <t>701985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>760775</t>
+          <t>759841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159722</t>
+          <t>163593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207623</t>
+          <t>208981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100013</t>
+          <t>99227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137766</t>
+          <t>137321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274014</t>
+          <t>274948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333017</t>
+          <t>332804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253026</t>
+          <t>252867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>287982</t>
+          <t>289744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282524</t>
+          <t>282958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>317311</t>
+          <t>316937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>545608</t>
+          <t>544365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>595231</t>
+          <t>598499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97894</t>
+          <t>96132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132850</t>
+          <t>133009</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86675</t>
+          <t>87049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121462</t>
+          <t>121028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194631</t>
+          <t>191363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>244254</t>
+          <t>245497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195955</t>
+          <t>196553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>226392</t>
+          <t>226204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252228</t>
+          <t>252220</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>281829</t>
+          <t>280761</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>458481</t>
+          <t>458618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>500892</t>
+          <t>499912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66191</t>
+          <t>66379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96628</t>
+          <t>96030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>62173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90706</t>
+          <t>90714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134625</t>
+          <t>135605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177036</t>
+          <t>176899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143974</t>
+          <t>145211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168739</t>
+          <t>168275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>80,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>258279</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>240307</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>274683</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>82,26%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>416229</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>396214</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>437212</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>72,86%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>80,4%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>258279</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>240749</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>272690</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>77,35%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>72,1%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>416229</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>395329</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>435125</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>72,7%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>41608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65909</t>
+          <t>64672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>30,81%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>75629</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>59225</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>93601</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>28,03%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>127562</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>106579</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>147577</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>19,6%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>75629</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>61218</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>93159</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>127562</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>108666</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>148462</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2013745</t>
+          <t>2020508</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2128375</t>
+          <t>2125928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2341215</t>
+          <t>2344836</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2449848</t>
+          <t>2451375</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4397999</t>
+          <t>4385114</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4555090</t>
+          <t>4542259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1147334</t>
+          <t>1149781</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1261964</t>
+          <t>1255201</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>928289</t>
+          <t>926762</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1036922</t>
+          <t>1033301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2098757</t>
+          <t>2111588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2255848</t>
+          <t>2268733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>211378</t>
+          <t>212746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254902</t>
+          <t>254490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>254819</t>
+          <t>251957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>293385</t>
+          <t>292691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>477643</t>
+          <t>478066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>534521</t>
+          <t>536021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199244</t>
+          <t>199656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242768</t>
+          <t>241400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135903</t>
+          <t>136597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174469</t>
+          <t>177331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>348913</t>
+          <t>347413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405791</t>
+          <t>405368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>436912</t>
+          <t>435622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>486956</t>
+          <t>485446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435178</t>
+          <t>438371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>480453</t>
+          <t>483208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>882151</t>
+          <t>884649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951104</t>
+          <t>953214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200131</t>
+          <t>201641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250175</t>
+          <t>251465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129802</t>
+          <t>127047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175077</t>
+          <t>171884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346238</t>
+          <t>344128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>415191</t>
+          <t>412693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>477485</t>
+          <t>474926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>521888</t>
+          <t>521986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>549468</t>
+          <t>552554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>594437</t>
+          <t>595354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1038882</t>
+          <t>1040794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1106683</t>
+          <t>1105142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158945</t>
+          <t>158847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203348</t>
+          <t>205907</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115430</t>
+          <t>114513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160399</t>
+          <t>157313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284017</t>
+          <t>285558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>351818</t>
+          <t>349906</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>420574</t>
+          <t>422154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>466365</t>
+          <t>467981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>486492</t>
+          <t>485590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>526886</t>
+          <t>525899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>919042</t>
+          <t>921508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>984403</t>
+          <t>981587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,15%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146212</t>
+          <t>144596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192003</t>
+          <t>190423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85167</t>
+          <t>86154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125561</t>
+          <t>126463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240227</t>
+          <t>243043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305588</t>
+          <t>303122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>312581</t>
+          <t>312758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>348603</t>
+          <t>348212</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>350140</t>
+          <t>347987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>383018</t>
+          <t>383243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672697</t>
+          <t>674305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>722300</t>
+          <t>723122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80826</t>
+          <t>81217</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116848</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62948</t>
+          <t>62723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95826</t>
+          <t>97979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153095</t>
+          <t>152273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>202698</t>
+          <t>201090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>236291</t>
+          <t>236583</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>264032</t>
+          <t>263460</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>295046</t>
+          <t>295541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319825</t>
+          <t>320394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>541968</t>
+          <t>541079</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579036</t>
+          <t>579360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42685</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70426</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34171</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58950</t>
+          <t>58455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81677</t>
+          <t>81353</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118745</t>
+          <t>119634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197163</t>
+          <t>197722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222118</t>
+          <t>222915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>315476</t>
+          <t>314277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>344702</t>
+          <t>343230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>520009</t>
+          <t>519316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>556197</t>
+          <t>557037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26664</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>51060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42350</t>
+          <t>43822</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71576</t>
+          <t>72775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79637</t>
+          <t>78797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>116518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2376920</t>
+          <t>2378762</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2486475</t>
+          <t>2487264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2772253</t>
+          <t>2770591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2868338</t>
+          <t>2869215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5181387</t>
+          <t>5183933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5330806</t>
+          <t>5328090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>933096</t>
+          <t>932307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1042651</t>
+          <t>1040809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>680139</t>
+          <t>679262</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776224</t>
+          <t>777886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1637243</t>
+          <t>1639959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1786662</t>
+          <t>1784116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235245</t>
+          <t>233485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>275338</t>
+          <t>274960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229535</t>
+          <t>228057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267507</t>
+          <t>267316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>479402</t>
+          <t>476808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>533383</t>
+          <t>531658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140922</t>
+          <t>141300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181015</t>
+          <t>182775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>126508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164289</t>
+          <t>165767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276701</t>
+          <t>278426</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>330682</t>
+          <t>333276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380488</t>
+          <t>382937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>423785</t>
+          <t>426315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>385963</t>
+          <t>382872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>426422</t>
+          <t>424380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>777136</t>
+          <t>777013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>839273</t>
+          <t>836826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164678</t>
+          <t>162148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207975</t>
+          <t>205526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133300</t>
+          <t>135342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173759</t>
+          <t>176850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308913</t>
+          <t>311360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371050</t>
+          <t>371173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>449372</t>
+          <t>450280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>496989</t>
+          <t>499425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>491536</t>
+          <t>491717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>534010</t>
+          <t>536063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>958093</t>
+          <t>955948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1017816</t>
+          <t>1018862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171165</t>
+          <t>168729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218782</t>
+          <t>217874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125383</t>
+          <t>123330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167857</t>
+          <t>167676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309731</t>
+          <t>308685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369454</t>
+          <t>371599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>432024</t>
+          <t>430535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476518</t>
+          <t>478856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>497955</t>
+          <t>499278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>538649</t>
+          <t>540438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>943227</t>
+          <t>942777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1004487</t>
+          <t>1006654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162496</t>
+          <t>160158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206990</t>
+          <t>208479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108227</t>
+          <t>106438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148921</t>
+          <t>147598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281403</t>
+          <t>279236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342663</t>
+          <t>343113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>348728</t>
+          <t>351154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>386747</t>
+          <t>388656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>387959</t>
+          <t>389800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>425130</t>
+          <t>424922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>748965</t>
+          <t>750928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>802422</t>
+          <t>803024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88129</t>
+          <t>86220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126148</t>
+          <t>123722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68330</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105501</t>
+          <t>103660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>165913</t>
+          <t>165311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219370</t>
+          <t>217407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>253266</t>
+          <t>254121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>282842</t>
+          <t>282915</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>303367</t>
+          <t>302917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331939</t>
+          <t>331171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>567115</t>
+          <t>566934</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>605925</t>
+          <t>607393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50491</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80140</t>
+          <t>79285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43748</t>
+          <t>44516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>72770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103168</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141978</t>
+          <t>142159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>201724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224093</t>
+          <t>223945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298041</t>
+          <t>298523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>334852</t>
+          <t>334446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>508802</t>
+          <t>506761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>550619</t>
+          <t>549927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>33053</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54594</t>
+          <t>55274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63970</t>
+          <t>64376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>100781</t>
+          <t>100299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105201</t>
+          <t>105893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147018</t>
+          <t>149059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2389348</t>
+          <t>2392468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2491913</t>
+          <t>2498647</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2683182</t>
+          <t>2676208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2780348</t>
+          <t>2778115</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5097210</t>
+          <t>5092834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5246277</t>
+          <t>5239708</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>885258</t>
+          <t>878524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>987823</t>
+          <t>984703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>747436</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>844602</t>
+          <t>851576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1658679</t>
+          <t>1665248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1807746</t>
+          <t>1812122</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>362717</t>
+          <t>375427</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>336691</t>
+          <t>353074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>378933</t>
+          <t>390276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>284493</t>
+          <t>332994</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>263466</t>
+          <t>315468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>296785</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>647210</t>
+          <t>708421</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615663</t>
+          <t>681729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>668159</t>
+          <t>729354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>17517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>54719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>65977</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>401827</t>
+          <t>450457</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>386837</t>
+          <t>435121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>411426</t>
+          <t>461697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>488829</t>
+          <t>477269</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>475481</t>
+          <t>465845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>498427</t>
+          <t>485489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>890656</t>
+          <t>927727</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>872259</t>
+          <t>910504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904559</t>
+          <t>942088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>34263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934180</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>503213</t>
+          <t>584275</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>489788</t>
+          <t>569206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>513219</t>
+          <t>594784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>519681</t>
+          <t>598500</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>510103</t>
+          <t>588955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>526235</t>
+          <t>605993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1022893</t>
+          <t>1182775</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1006590</t>
+          <t>1164004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1035558</t>
+          <t>1196080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32962</t>
+          <t>35444</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22787</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16233</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55749</t>
+          <t>59083</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>45778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>77854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536175</t>
+          <t>619719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078642</t>
+          <t>1241858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>852813</t>
+          <t>665011</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>832205</t>
+          <t>651310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>873470</t>
+          <t>675631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>686008</t>
+          <t>707887</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>677646</t>
+          <t>698928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>693174</t>
+          <t>714899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1538821</t>
+          <t>1372897</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1518280</t>
+          <t>1357769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1561250</t>
+          <t>1385822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>35606</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>63457</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38346</t>
+          <t>50532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81316</t>
+          <t>78585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599596</t>
+          <t>1436354</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>521815</t>
+          <t>569322</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>506974</t>
+          <t>556610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>531588</t>
+          <t>579608</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>528335</t>
+          <t>587541</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>521255</t>
+          <t>579175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534357</t>
+          <t>593858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1050150</t>
+          <t>1156863</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1034054</t>
+          <t>1141908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1061005</t>
+          <t>1168532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52522</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>21314</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>57251</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46396</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559496</t>
+          <t>607544</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107401</t>
+          <t>1216399</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>349911</t>
+          <t>386409</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>342016</t>
+          <t>378538</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>356336</t>
+          <t>393369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>593929</t>
+          <t>422926</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>584199</t>
+          <t>415785</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>603234</t>
+          <t>427518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>943840</t>
+          <t>809335</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>931371</t>
+          <t>797650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>960328</t>
+          <t>818331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25342</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>15125</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367358</t>
+          <t>406075</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607273</t>
+          <t>438051</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974631</t>
+          <t>844126</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>271604</t>
+          <t>298349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>264786</t>
+          <t>291789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276017</t>
+          <t>303053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>406939</t>
+          <t>444841</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>400154</t>
+          <t>437462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>412312</t>
+          <t>450259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>678542</t>
+          <t>743190</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>669575</t>
+          <t>734986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>685805</t>
+          <t>751145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>28063</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37030</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282018</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424588</t>
+          <t>463333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>772763</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3225292</t>
+          <t>3298351</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3308458</t>
+          <t>3361511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3481519</t>
+          <t>3547249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3538720</t>
+          <t>3595058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6717872</t>
+          <t>6856932</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6824431</t>
+          <t>6937159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P36B08_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2023 (tasa de respuesta: 99,86%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
